--- a/public/downloads/NTUB_學分修業與證書資格試算表.xlsx
+++ b/public/downloads/NTUB_學分修業與證書資格試算表.xlsx
@@ -491,28 +491,28 @@
         <v>15</v>
       </c>
       <c r="E5">
-        <f>=!F20</f>
+        <f>!F22</f>
       </c>
       <c r="F5">
         <v>2</v>
       </c>
       <c r="G5">
-        <f>=!F21</f>
+        <f>!F23</f>
       </c>
       <c r="H5">
         <v>13</v>
       </c>
       <c r="I5">
-        <f>=!F22</f>
+        <f>!F24</f>
       </c>
       <c r="J5" t="str">
         <v>需跨修至少1門外系</v>
       </c>
       <c r="K5">
-        <f>=!F24</f>
+        <f>!F26</f>
       </c>
       <c r="L5">
-        <f>=IF(AND(E5&gt;=D5, G5&gt;=F5, IF(J5="需跨修至少1門外系", K5&gt;=1, TRUE)), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
+        <f>IF(AND(E5&gt;=D5, G5&gt;=F5, IF(J5="需跨修至少1門外系", K5&gt;=1, TRUE)), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
       </c>
       <c r="M5" t="str">
         <v>企業永續經營管理</v>
@@ -532,28 +532,28 @@
         <v>15</v>
       </c>
       <c r="E6">
-        <f>=!F21</f>
+        <f>!F23</f>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
       <c r="G6">
-        <f>=!F22</f>
+        <f>!F24</f>
       </c>
       <c r="H6">
         <v>13</v>
       </c>
       <c r="I6">
-        <f>=!F23</f>
+        <f>!F25</f>
       </c>
       <c r="J6" t="str">
         <v>需跨修至少1門外系</v>
       </c>
       <c r="K6">
-        <f>=!F25</f>
+        <f>!F27</f>
       </c>
       <c r="L6">
-        <f>=IF(AND(E6&gt;=D6, G6&gt;=F6, IF(J6="需跨修至少1門外系", K6&gt;=1, TRUE)), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
+        <f>IF(AND(E6&gt;=D6, G6&gt;=F6, IF(J6="需跨修至少1門外系", K6&gt;=1, TRUE)), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
       </c>
       <c r="M6" t="str">
         <v>創新與創業管理</v>
@@ -573,28 +573,28 @@
         <v>15</v>
       </c>
       <c r="E7">
-        <f>=!F33</f>
+        <f>!F35</f>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7">
-        <f>=!F34</f>
+        <f>!F36</f>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7">
-        <f>=!F35</f>
+        <f>!F37</f>
       </c>
       <c r="J7" t="str">
         <v>需跨修至少1門外系</v>
       </c>
       <c r="K7">
-        <f>=!F37</f>
+        <f>!F39</f>
       </c>
       <c r="L7">
-        <f>=IF(AND(E7&gt;=D7, G7&gt;=F7, IF(J7="需跨修至少1門外系", K7&gt;=1, TRUE)), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
+        <f>IF(AND(E7&gt;=D7, G7&gt;=F7, IF(J7="需跨修至少1門外系", K7&gt;=1, TRUE)), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
       </c>
       <c r="M7" t="str">
         <v>外語與商務</v>
@@ -614,28 +614,28 @@
         <v>8</v>
       </c>
       <c r="E8">
-        <f>=!F20</f>
+        <f>!F22</f>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8">
-        <f>=!F21</f>
+        <f>!F23</f>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <f>=!F22</f>
+        <f>!F24</f>
       </c>
       <c r="J8" t="str">
         <v>需跨修至少1門外系</v>
       </c>
       <c r="K8">
-        <f>=!F24</f>
+        <f>!F26</f>
       </c>
       <c r="L8">
-        <f>=IF(AND(E8&gt;=D8, G8&gt;=F8, IF(J8="需跨修至少1門外系", K8&gt;=1, TRUE)), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
+        <f>IF(AND(E8&gt;=D8, G8&gt;=F8, IF(J8="需跨修至少1門外系", K8&gt;=1, TRUE)), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
       </c>
       <c r="M8" t="str">
         <v>大數據</v>
@@ -655,28 +655,28 @@
         <v>15</v>
       </c>
       <c r="E9">
-        <f>=!F24</f>
+        <f>!F26</f>
       </c>
       <c r="F9">
         <v>2</v>
       </c>
       <c r="G9">
-        <f>=!F25</f>
+        <f>!F27</f>
       </c>
       <c r="H9">
         <v>13</v>
       </c>
       <c r="I9">
-        <f>=!F26</f>
+        <f>!F28</f>
       </c>
       <c r="J9" t="str">
         <v>需跨修至少1門外系</v>
       </c>
       <c r="K9">
-        <f>=!F28</f>
+        <f>!F30</f>
       </c>
       <c r="L9">
-        <f>=IF(AND(E9&gt;=D9, G9&gt;=F9, IF(J9="需跨修至少1門外系", K9&gt;=1, TRUE)), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
+        <f>IF(AND(E9&gt;=D9, G9&gt;=F9, IF(J9="需跨修至少1門外系", K9&gt;=1, TRUE)), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
       </c>
       <c r="M9" t="str">
         <v>數位行銷</v>
@@ -696,28 +696,28 @@
         <v>8</v>
       </c>
       <c r="E10">
-        <f>=!F19</f>
+        <f>!F21</f>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
       <c r="G10">
-        <f>=!F20</f>
+        <f>!F22</f>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
-        <f>=!F21</f>
+        <f>!F23</f>
       </c>
       <c r="J10" t="str">
         <v>需跨修至少1門外系</v>
       </c>
       <c r="K10">
-        <f>=!F23</f>
+        <f>!F25</f>
       </c>
       <c r="L10">
-        <f>=IF(AND(E10&gt;=D10, G10&gt;=F10, IF(J10="需跨修至少1門外系", K10&gt;=1, TRUE)), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
+        <f>IF(AND(E10&gt;=D10, G10&gt;=F10, IF(J10="需跨修至少1門外系", K10&gt;=1, TRUE)), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
       </c>
       <c r="M10" t="str">
         <v>數位行銷與語言科技應用</v>
@@ -737,28 +737,28 @@
         <v>8</v>
       </c>
       <c r="E11">
-        <f>=!F27</f>
+        <f>!F29</f>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
-        <f>=!F28</f>
+        <f>!F30</f>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <f>=!F29</f>
+        <f>!F31</f>
       </c>
       <c r="J11" t="str">
         <v>需跨修至少1門外系</v>
       </c>
       <c r="K11">
-        <f>=!F31</f>
+        <f>!F33</f>
       </c>
       <c r="L11">
-        <f>=IF(AND(E11&gt;=D11, G11&gt;=F11, IF(J11="需跨修至少1門外系", K11&gt;=1, TRUE)), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
+        <f>IF(AND(E11&gt;=D11, G11&gt;=F11, IF(J11="需跨修至少1門外系", K11&gt;=1, TRUE)), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
       </c>
       <c r="M11" t="str">
         <v>數據分析與視覺化</v>
@@ -778,28 +778,28 @@
         <v>12</v>
       </c>
       <c r="E12">
-        <f>=!F20</f>
+        <f>!F22</f>
       </c>
       <c r="F12">
         <v>0</v>
       </c>
       <c r="G12">
-        <f>=!F21</f>
+        <f>!F23</f>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12">
-        <f>=!F22</f>
+        <f>!F24</f>
       </c>
       <c r="J12" t="str">
         <v>需跨修至少1門外系</v>
       </c>
       <c r="K12">
-        <f>=!F24</f>
+        <f>!F26</f>
       </c>
       <c r="L12">
-        <f>=IF(AND(E12&gt;=D12, G12&gt;=F12, IF(J12="需跨修至少1門外系", K12&gt;=1, TRUE)), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
+        <f>IF(AND(E12&gt;=D12, G12&gt;=F12, IF(J12="需跨修至少1門外系", K12&gt;=1, TRUE)), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
       </c>
       <c r="M12" t="str">
         <v>社群媒體行銷</v>
@@ -819,28 +819,28 @@
         <v>8</v>
       </c>
       <c r="E13">
-        <f>=!F24</f>
+        <f>!F26</f>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
       <c r="G13">
-        <f>=!F25</f>
+        <f>!F27</f>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13">
-        <f>=!F26</f>
+        <f>!F28</f>
       </c>
       <c r="J13" t="str">
         <v>需跨修至少1門外系</v>
       </c>
       <c r="K13">
-        <f>=!F28</f>
+        <f>!F30</f>
       </c>
       <c r="L13">
-        <f>=IF(AND(E13&gt;=D13, G13&gt;=F13, IF(J13="需跨修至少1門外系", K13&gt;=1, TRUE)), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
+        <f>IF(AND(E13&gt;=D13, G13&gt;=F13, IF(J13="需跨修至少1門外系", K13&gt;=1, TRUE)), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
       </c>
       <c r="M13" t="str">
         <v>東亞語言與商務</v>
@@ -879,7 +879,7 @@
     <col min="5" max="5" width="10.83203125" customWidth="1"/>
     <col min="6" max="6" width="10.83203125" customWidth="1"/>
     <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
     <col min="9" max="9" width="25.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1355,7 +1355,7 @@
         <v/>
       </c>
       <c r="F22">
-        <f>=SUMIF(A6:A19, TRUE, F6:F19)</f>
+        <f>SUMIF(A6:A19, TRUE, F6:F19)</f>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1381,7 +1381,7 @@
         <v/>
       </c>
       <c r="F23">
-        <f>=SUMIFS(F6:F19, A6:A19, TRUE, E6:E19, "必修")</f>
+        <f>SUMIFS(F6:F19, A6:A19, TRUE, E6:E19, "必修")</f>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1407,7 +1407,7 @@
         <v/>
       </c>
       <c r="F24">
-        <f>=SUMIFS(F6:F19, A6:A19, TRUE, E6:E19, "選修")</f>
+        <f>SUMIFS(F6:F19, A6:A19, TRUE, E6:E19, "選修")</f>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v/>
       </c>
       <c r="F25">
-        <f>=SUMIFS(F6:F19, A6:A19, TRUE, H6:H19, "本系 (資管)")</f>
+        <f>SUMIFS(F6:F19, A6:A19, TRUE, H6:H19, "本系 (資訊管理系)")</f>
       </c>
     </row>
     <row r="26">
@@ -1453,7 +1453,7 @@
         <v/>
       </c>
       <c r="F26">
-        <f>=COUNTIFS(A6:A19, TRUE, H6:H19, "外系/跨系")</f>
+        <f>COUNTIFS(A6:A19, TRUE, H6:H19, "外系/跨系")</f>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1479,7 +1479,7 @@
         <v/>
       </c>
       <c r="F27">
-        <f>=IF(AND(F22&gt;=12, F23&gt;=0, IF("true"="true", F26&gt;=1, TRUE)), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
+        <f>IF(AND(F22&gt;=12, F23&gt;=0, F26&gt;=1), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
       </c>
     </row>
   </sheetData>
@@ -1500,7 +1500,7 @@
     <col min="5" max="5" width="10.83203125" customWidth="1"/>
     <col min="6" max="6" width="10.83203125" customWidth="1"/>
     <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
     <col min="9" max="9" width="25.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2092,7 +2092,7 @@
         <v/>
       </c>
       <c r="F26">
-        <f>=SUMIF(A6:A23, TRUE, F6:F23)</f>
+        <f>SUMIF(A6:A23, TRUE, F6:F23)</f>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -2118,7 +2118,7 @@
         <v/>
       </c>
       <c r="F27">
-        <f>=SUMIFS(F6:F23, A6:A23, TRUE, E6:E23, "必修")</f>
+        <f>SUMIFS(F6:F23, A6:A23, TRUE, E6:E23, "必修")</f>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -2144,7 +2144,7 @@
         <v/>
       </c>
       <c r="F28">
-        <f>=SUMIFS(F6:F23, A6:A23, TRUE, E6:E23, "選修")</f>
+        <f>SUMIFS(F6:F23, A6:A23, TRUE, E6:E23, "選修")</f>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -2170,7 +2170,7 @@
         <v/>
       </c>
       <c r="F29">
-        <f>=SUMIFS(F6:F23, A6:A23, TRUE, H6:H23, "本系 (資管)")</f>
+        <f>SUMIFS(F6:F23, A6:A23, TRUE, H6:H23, "本系 (資訊管理系)")</f>
       </c>
     </row>
     <row r="30">
@@ -2190,7 +2190,7 @@
         <v/>
       </c>
       <c r="F30">
-        <f>=COUNTIFS(A6:A23, TRUE, H6:H23, "外系/跨系")</f>
+        <f>COUNTIFS(A6:A23, TRUE, H6:H23, "外系/跨系")</f>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -2216,7 +2216,7 @@
         <v/>
       </c>
       <c r="F31">
-        <f>=IF(AND(F26&gt;=8, F27&gt;=0, IF("true"="true", F30&gt;=1, TRUE)), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
+        <f>IF(AND(F26&gt;=8, F27&gt;=0, F30&gt;=1), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
       </c>
     </row>
   </sheetData>
@@ -2781,7 +2781,7 @@
         <v/>
       </c>
       <c r="F12">
-        <f>=SUMIF(A5:A9, TRUE, F5:F9)</f>
+        <f>SUMIF(A5:A9, TRUE, F5:F9)</f>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -2808,7 +2808,7 @@
     <col min="5" max="5" width="10.83203125" customWidth="1"/>
     <col min="6" max="6" width="10.83203125" customWidth="1"/>
     <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
     <col min="9" max="9" width="35.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4585,7 +4585,7 @@
         <v>全學年</v>
       </c>
       <c r="H64" t="str">
-        <v>本系 (資管)</v>
+        <v>本系 (資訊管理系)</v>
       </c>
       <c r="I64" t="str">
         <v>大數據微學程</v>
@@ -4759,7 +4759,7 @@
         <v>全學年</v>
       </c>
       <c r="H70" t="str">
-        <v>本系 (資管)</v>
+        <v>本系 (資訊管理系)</v>
       </c>
       <c r="I70" t="str">
         <v>大數據微學程</v>
@@ -4788,7 +4788,7 @@
         <v>全學年</v>
       </c>
       <c r="H71" t="str">
-        <v>本系 (資管)</v>
+        <v>本系 (資訊管理系)</v>
       </c>
       <c r="I71" t="str">
         <v>大數據微學程</v>
@@ -4817,7 +4817,7 @@
         <v>全學年</v>
       </c>
       <c r="H72" t="str">
-        <v>本系 (資管)</v>
+        <v>本系 (資訊管理系)</v>
       </c>
       <c r="I72" t="str">
         <v>大數據微學程</v>
@@ -4933,7 +4933,7 @@
         <v>全學年</v>
       </c>
       <c r="H76" t="str">
-        <v>本系 (資管)</v>
+        <v>本系 (資訊管理系)</v>
       </c>
       <c r="I76" t="str">
         <v>數位行銷學分學程</v>
@@ -5223,7 +5223,7 @@
         <v>全學年</v>
       </c>
       <c r="H86" t="str">
-        <v>本系 (資管)</v>
+        <v>本系 (資訊管理系)</v>
       </c>
       <c r="I86" t="str">
         <v>數位行銷學分學程</v>
@@ -5252,7 +5252,7 @@
         <v>全學年</v>
       </c>
       <c r="H87" t="str">
-        <v>本系 (資管)</v>
+        <v>本系 (資訊管理系)</v>
       </c>
       <c r="I87" t="str">
         <v>數位行銷學分學程</v>
@@ -5281,7 +5281,7 @@
         <v>全學年</v>
       </c>
       <c r="H88" t="str">
-        <v>本系 (資管)</v>
+        <v>本系 (資訊管理系)</v>
       </c>
       <c r="I88" t="str">
         <v>數位行銷學分學程</v>
@@ -6093,7 +6093,7 @@
         <v>全學年</v>
       </c>
       <c r="H116" t="str">
-        <v>本系 (資管)</v>
+        <v>本系 (資訊管理系)</v>
       </c>
       <c r="I116" t="str">
         <v>數據分析與視覺化微學程</v>
@@ -6122,7 +6122,7 @@
         <v>全學年</v>
       </c>
       <c r="H117" t="str">
-        <v>本系 (資管)</v>
+        <v>本系 (資訊管理系)</v>
       </c>
       <c r="I117" t="str">
         <v>數據分析與視覺化微學程</v>
@@ -6151,7 +6151,7 @@
         <v>全學年</v>
       </c>
       <c r="H118" t="str">
-        <v>本系 (資管)</v>
+        <v>本系 (資訊管理系)</v>
       </c>
       <c r="I118" t="str">
         <v>數據分析與視覺化微學程</v>
@@ -6180,7 +6180,7 @@
         <v>全學年</v>
       </c>
       <c r="H119" t="str">
-        <v>本系 (資管)</v>
+        <v>本系 (資訊管理系)</v>
       </c>
       <c r="I119" t="str">
         <v>數據分析與視覺化微學程</v>
@@ -6209,7 +6209,7 @@
         <v>全學年</v>
       </c>
       <c r="H120" t="str">
-        <v>本系 (資管)</v>
+        <v>本系 (資訊管理系)</v>
       </c>
       <c r="I120" t="str">
         <v>數據分析與視覺化微學程</v>
@@ -6238,7 +6238,7 @@
         <v>全學年</v>
       </c>
       <c r="H121" t="str">
-        <v>本系 (資管)</v>
+        <v>本系 (資訊管理系)</v>
       </c>
       <c r="I121" t="str">
         <v>數據分析與視覺化微學程</v>
@@ -6267,7 +6267,7 @@
         <v>全學年</v>
       </c>
       <c r="H122" t="str">
-        <v>本系 (資管)</v>
+        <v>本系 (資訊管理系)</v>
       </c>
       <c r="I122" t="str">
         <v>數據分析與視覺化微學程</v>
@@ -6296,7 +6296,7 @@
         <v>全學年</v>
       </c>
       <c r="H123" t="str">
-        <v>本系 (資管)</v>
+        <v>本系 (資訊管理系)</v>
       </c>
       <c r="I123" t="str">
         <v>數據分析與視覺化微學程</v>
@@ -6325,7 +6325,7 @@
         <v>全學年</v>
       </c>
       <c r="H124" t="str">
-        <v>本系 (資管)</v>
+        <v>本系 (資訊管理系)</v>
       </c>
       <c r="I124" t="str">
         <v>數據分析與視覺化微學程</v>
@@ -6354,7 +6354,7 @@
         <v>全學年</v>
       </c>
       <c r="H125" t="str">
-        <v>本系 (資管)</v>
+        <v>本系 (資訊管理系)</v>
       </c>
       <c r="I125" t="str">
         <v>數據分析與視覺化微學程</v>
@@ -6383,7 +6383,7 @@
         <v>全學年</v>
       </c>
       <c r="H126" t="str">
-        <v>本系 (資管)</v>
+        <v>本系 (資訊管理系)</v>
       </c>
       <c r="I126" t="str">
         <v>數據分析與視覺化微學程</v>
@@ -7339,7 +7339,7 @@
         <v/>
       </c>
       <c r="F161">
-        <f>=SUMIF(A5:A158, TRUE, F5:F158)</f>
+        <f>SUMIF(A5:A158, TRUE, F5:F158)</f>
       </c>
       <c r="G161" t="str">
         <v/>
@@ -7365,7 +7365,7 @@
         <v/>
       </c>
       <c r="F162">
-        <f>=SUMIFS(F5:F158, A5:A158, TRUE, E5:E158, "必修")</f>
+        <f>SUMIFS(F5:F158, A5:A158, TRUE, E5:E158, "必修")</f>
       </c>
     </row>
     <row r="163">
@@ -7385,7 +7385,7 @@
         <v/>
       </c>
       <c r="F163">
-        <f>=SUMIFS(F5:F158, A5:A158, TRUE, E5:E158, "選修")</f>
+        <f>SUMIFS(F5:F158, A5:A158, TRUE, E5:E158, "選修")</f>
       </c>
     </row>
     <row r="164">
@@ -7405,7 +7405,7 @@
         <v/>
       </c>
       <c r="F164">
-        <f>=SUMIFS(F5:F158, A5:A158, TRUE, H5:H158, "本系 (資管)")</f>
+        <f>SUMIFS(F5:F158, A5:A158, TRUE, H5:H158, "本系 (資訊管理系)")</f>
       </c>
     </row>
     <row r="165">
@@ -7425,7 +7425,7 @@
         <v/>
       </c>
       <c r="F165">
-        <f>=SUMIFS(F5:F158, A5:A158, TRUE, H5:H158, "外系/跨系")</f>
+        <f>SUMIFS(F5:F158, A5:A158, TRUE, H5:H158, "外系/跨系")</f>
       </c>
     </row>
   </sheetData>
@@ -7446,7 +7446,7 @@
     <col min="5" max="5" width="10.83203125" customWidth="1"/>
     <col min="6" max="6" width="10.83203125" customWidth="1"/>
     <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
     <col min="9" max="9" width="25.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7922,7 +7922,7 @@
         <v/>
       </c>
       <c r="F22">
-        <f>=SUMIF(A6:A19, TRUE, F6:F19)</f>
+        <f>SUMIF(A6:A19, TRUE, F6:F19)</f>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -7948,7 +7948,7 @@
         <v/>
       </c>
       <c r="F23">
-        <f>=SUMIFS(F6:F19, A6:A19, TRUE, E6:E19, "必修")</f>
+        <f>SUMIFS(F6:F19, A6:A19, TRUE, E6:E19, "必修")</f>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -7974,7 +7974,7 @@
         <v/>
       </c>
       <c r="F24">
-        <f>=SUMIFS(F6:F19, A6:A19, TRUE, E6:E19, "選修")</f>
+        <f>SUMIFS(F6:F19, A6:A19, TRUE, E6:E19, "選修")</f>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -8000,7 +8000,7 @@
         <v/>
       </c>
       <c r="F25">
-        <f>=SUMIFS(F6:F19, A6:A19, TRUE, H6:H19, "本系 (資管)")</f>
+        <f>SUMIFS(F6:F19, A6:A19, TRUE, H6:H19, "本系 (資訊管理系)")</f>
       </c>
     </row>
     <row r="26">
@@ -8020,7 +8020,7 @@
         <v/>
       </c>
       <c r="F26">
-        <f>=COUNTIFS(A6:A19, TRUE, H6:H19, "外系/跨系")</f>
+        <f>COUNTIFS(A6:A19, TRUE, H6:H19, "外系/跨系")</f>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -8046,7 +8046,7 @@
         <v/>
       </c>
       <c r="F27">
-        <f>=IF(AND(F22&gt;=15, F23&gt;=2, IF("true"="true", F26&gt;=1, TRUE)), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
+        <f>IF(AND(F22&gt;=15, F23&gt;=2, F26&gt;=1), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
       </c>
     </row>
   </sheetData>
@@ -8067,7 +8067,7 @@
     <col min="5" max="5" width="10.83203125" customWidth="1"/>
     <col min="6" max="6" width="10.83203125" customWidth="1"/>
     <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
     <col min="9" max="9" width="25.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8572,7 +8572,7 @@
         <v/>
       </c>
       <c r="F23">
-        <f>=SUMIF(A6:A20, TRUE, F6:F20)</f>
+        <f>SUMIF(A6:A20, TRUE, F6:F20)</f>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -8598,7 +8598,7 @@
         <v/>
       </c>
       <c r="F24">
-        <f>=SUMIFS(F6:F20, A6:A20, TRUE, E6:E20, "必修")</f>
+        <f>SUMIFS(F6:F20, A6:A20, TRUE, E6:E20, "必修")</f>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -8624,7 +8624,7 @@
         <v/>
       </c>
       <c r="F25">
-        <f>=SUMIFS(F6:F20, A6:A20, TRUE, E6:E20, "選修")</f>
+        <f>SUMIFS(F6:F20, A6:A20, TRUE, E6:E20, "選修")</f>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -8650,7 +8650,7 @@
         <v/>
       </c>
       <c r="F26">
-        <f>=SUMIFS(F6:F20, A6:A20, TRUE, H6:H20, "本系 (資管)")</f>
+        <f>SUMIFS(F6:F20, A6:A20, TRUE, H6:H20, "本系 (資訊管理系)")</f>
       </c>
     </row>
     <row r="27">
@@ -8670,7 +8670,7 @@
         <v/>
       </c>
       <c r="F27">
-        <f>=COUNTIFS(A6:A20, TRUE, H6:H20, "外系/跨系")</f>
+        <f>COUNTIFS(A6:A20, TRUE, H6:H20, "外系/跨系")</f>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -8696,7 +8696,7 @@
         <v/>
       </c>
       <c r="F28">
-        <f>=IF(AND(F23&gt;=15, F24&gt;=2, IF("true"="true", F27&gt;=1, TRUE)), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
+        <f>IF(AND(F23&gt;=15, F24&gt;=2, F27&gt;=1), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
       </c>
     </row>
   </sheetData>
@@ -8717,7 +8717,7 @@
     <col min="5" max="5" width="10.83203125" customWidth="1"/>
     <col min="6" max="6" width="10.83203125" customWidth="1"/>
     <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
     <col min="9" max="9" width="25.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9570,7 +9570,7 @@
         <v/>
       </c>
       <c r="F35">
-        <f>=SUMIF(A6:A32, TRUE, F6:F32)</f>
+        <f>SUMIF(A6:A32, TRUE, F6:F32)</f>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -9596,7 +9596,7 @@
         <v/>
       </c>
       <c r="F36">
-        <f>=SUMIFS(F6:F32, A6:A32, TRUE, E6:E32, "必修")</f>
+        <f>SUMIFS(F6:F32, A6:A32, TRUE, E6:E32, "必修")</f>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -9622,7 +9622,7 @@
         <v/>
       </c>
       <c r="F37">
-        <f>=SUMIFS(F6:F32, A6:A32, TRUE, E6:E32, "選修")</f>
+        <f>SUMIFS(F6:F32, A6:A32, TRUE, E6:E32, "選修")</f>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -9648,7 +9648,7 @@
         <v/>
       </c>
       <c r="F38">
-        <f>=SUMIFS(F6:F32, A6:A32, TRUE, H6:H32, "本系 (資管)")</f>
+        <f>SUMIFS(F6:F32, A6:A32, TRUE, H6:H32, "本系 (資訊管理系)")</f>
       </c>
     </row>
     <row r="39">
@@ -9668,7 +9668,7 @@
         <v/>
       </c>
       <c r="F39">
-        <f>=COUNTIFS(A6:A32, TRUE, H6:H32, "外系/跨系")</f>
+        <f>COUNTIFS(A6:A32, TRUE, H6:H32, "外系/跨系")</f>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -9694,7 +9694,7 @@
         <v/>
       </c>
       <c r="F40">
-        <f>=IF(AND(F35&gt;=15, F36&gt;=0, IF("true"="true", F39&gt;=1, TRUE)), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
+        <f>IF(AND(F35&gt;=15, F36&gt;=0, F39&gt;=1), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
       </c>
     </row>
   </sheetData>
@@ -9715,7 +9715,7 @@
     <col min="5" max="5" width="10.83203125" customWidth="1"/>
     <col min="6" max="6" width="10.83203125" customWidth="1"/>
     <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
     <col min="9" max="9" width="25.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9873,7 +9873,7 @@
         <v>依學期開設</v>
       </c>
       <c r="H9" t="str">
-        <v>本系 (資管)</v>
+        <v>本系 (資訊管理系)</v>
       </c>
       <c r="I9" t="str">
         <v>核心必修</v>
@@ -10047,7 +10047,7 @@
         <v>依學期開設</v>
       </c>
       <c r="H15" t="str">
-        <v>本系 (資管)</v>
+        <v>本系 (資訊管理系)</v>
       </c>
       <c r="I15" t="str">
         <v>進階專業</v>
@@ -10076,7 +10076,7 @@
         <v>依學期開設</v>
       </c>
       <c r="H16" t="str">
-        <v>本系 (資管)</v>
+        <v>本系 (資訊管理系)</v>
       </c>
       <c r="I16" t="str">
         <v>進階專業</v>
@@ -10105,7 +10105,7 @@
         <v>依學期開設</v>
       </c>
       <c r="H17" t="str">
-        <v>本系 (資管)</v>
+        <v>本系 (資訊管理系)</v>
       </c>
       <c r="I17" t="str">
         <v>進階專業</v>
@@ -10191,7 +10191,7 @@
         <v/>
       </c>
       <c r="F22">
-        <f>=SUMIF(A6:A19, TRUE, F6:F19)</f>
+        <f>SUMIF(A6:A19, TRUE, F6:F19)</f>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -10217,7 +10217,7 @@
         <v/>
       </c>
       <c r="F23">
-        <f>=SUMIFS(F6:F19, A6:A19, TRUE, E6:E19, "必修")</f>
+        <f>SUMIFS(F6:F19, A6:A19, TRUE, E6:E19, "必修")</f>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -10243,7 +10243,7 @@
         <v/>
       </c>
       <c r="F24">
-        <f>=SUMIFS(F6:F19, A6:A19, TRUE, E6:E19, "選修")</f>
+        <f>SUMIFS(F6:F19, A6:A19, TRUE, E6:E19, "選修")</f>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -10269,7 +10269,7 @@
         <v/>
       </c>
       <c r="F25">
-        <f>=SUMIFS(F6:F19, A6:A19, TRUE, H6:H19, "本系 (資管)")</f>
+        <f>SUMIFS(F6:F19, A6:A19, TRUE, H6:H19, "本系 (資訊管理系)")</f>
       </c>
     </row>
     <row r="26">
@@ -10289,7 +10289,7 @@
         <v/>
       </c>
       <c r="F26">
-        <f>=COUNTIFS(A6:A19, TRUE, H6:H19, "外系/跨系")</f>
+        <f>COUNTIFS(A6:A19, TRUE, H6:H19, "外系/跨系")</f>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -10315,7 +10315,7 @@
         <v/>
       </c>
       <c r="F27">
-        <f>=IF(AND(F22&gt;=8, F23&gt;=0, IF("true"="true", F26&gt;=1, TRUE)), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
+        <f>IF(AND(F22&gt;=8, F23&gt;=0, F26&gt;=1), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
       </c>
     </row>
   </sheetData>
@@ -10336,7 +10336,7 @@
     <col min="5" max="5" width="10.83203125" customWidth="1"/>
     <col min="6" max="6" width="10.83203125" customWidth="1"/>
     <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
     <col min="9" max="9" width="25.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10436,7 +10436,7 @@
         <v>依學期開設</v>
       </c>
       <c r="H7" t="str">
-        <v>本系 (資管)</v>
+        <v>本系 (資訊管理系)</v>
       </c>
       <c r="I7" t="str">
         <v>專業選修</v>
@@ -10726,7 +10726,7 @@
         <v>依學期開設</v>
       </c>
       <c r="H17" t="str">
-        <v>本系 (資管)</v>
+        <v>本系 (資訊管理系)</v>
       </c>
       <c r="I17" t="str">
         <v>專業選修</v>
@@ -10755,7 +10755,7 @@
         <v>依學期開設</v>
       </c>
       <c r="H18" t="str">
-        <v>本系 (資管)</v>
+        <v>本系 (資訊管理系)</v>
       </c>
       <c r="I18" t="str">
         <v>專業選修</v>
@@ -10784,7 +10784,7 @@
         <v>依學期開設</v>
       </c>
       <c r="H19" t="str">
-        <v>本系 (資管)</v>
+        <v>本系 (資訊管理系)</v>
       </c>
       <c r="I19" t="str">
         <v>專業選修</v>
@@ -10928,7 +10928,7 @@
         <v/>
       </c>
       <c r="F26">
-        <f>=SUMIF(A6:A23, TRUE, F6:F23)</f>
+        <f>SUMIF(A6:A23, TRUE, F6:F23)</f>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -10954,7 +10954,7 @@
         <v/>
       </c>
       <c r="F27">
-        <f>=SUMIFS(F6:F23, A6:A23, TRUE, E6:E23, "必修")</f>
+        <f>SUMIFS(F6:F23, A6:A23, TRUE, E6:E23, "必修")</f>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -10980,7 +10980,7 @@
         <v/>
       </c>
       <c r="F28">
-        <f>=SUMIFS(F6:F23, A6:A23, TRUE, E6:E23, "選修")</f>
+        <f>SUMIFS(F6:F23, A6:A23, TRUE, E6:E23, "選修")</f>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -11006,7 +11006,7 @@
         <v/>
       </c>
       <c r="F29">
-        <f>=SUMIFS(F6:F23, A6:A23, TRUE, H6:H23, "本系 (資管)")</f>
+        <f>SUMIFS(F6:F23, A6:A23, TRUE, H6:H23, "本系 (資訊管理系)")</f>
       </c>
     </row>
     <row r="30">
@@ -11026,7 +11026,7 @@
         <v/>
       </c>
       <c r="F30">
-        <f>=COUNTIFS(A6:A23, TRUE, H6:H23, "外系/跨系")</f>
+        <f>COUNTIFS(A6:A23, TRUE, H6:H23, "外系/跨系")</f>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -11052,7 +11052,7 @@
         <v/>
       </c>
       <c r="F31">
-        <f>=IF(AND(F26&gt;=15, F27&gt;=2, IF("true"="true", F30&gt;=1, TRUE)), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
+        <f>IF(AND(F26&gt;=15, F27&gt;=2, F30&gt;=1), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
       </c>
     </row>
   </sheetData>
@@ -11073,7 +11073,7 @@
     <col min="5" max="5" width="10.83203125" customWidth="1"/>
     <col min="6" max="6" width="10.83203125" customWidth="1"/>
     <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
     <col min="9" max="9" width="25.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -11520,7 +11520,7 @@
         <v/>
       </c>
       <c r="F21">
-        <f>=SUMIF(A6:A18, TRUE, F6:F18)</f>
+        <f>SUMIF(A6:A18, TRUE, F6:F18)</f>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -11546,7 +11546,7 @@
         <v/>
       </c>
       <c r="F22">
-        <f>=SUMIFS(F6:F18, A6:A18, TRUE, E6:E18, "必修")</f>
+        <f>SUMIFS(F6:F18, A6:A18, TRUE, E6:E18, "必修")</f>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -11572,7 +11572,7 @@
         <v/>
       </c>
       <c r="F23">
-        <f>=SUMIFS(F6:F18, A6:A18, TRUE, E6:E18, "選修")</f>
+        <f>SUMIFS(F6:F18, A6:A18, TRUE, E6:E18, "選修")</f>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -11598,7 +11598,7 @@
         <v/>
       </c>
       <c r="F24">
-        <f>=SUMIFS(F6:F18, A6:A18, TRUE, H6:H18, "本系 (資管)")</f>
+        <f>SUMIFS(F6:F18, A6:A18, TRUE, H6:H18, "本系 (資訊管理系)")</f>
       </c>
     </row>
     <row r="25">
@@ -11618,7 +11618,7 @@
         <v/>
       </c>
       <c r="F25">
-        <f>=COUNTIFS(A6:A18, TRUE, H6:H18, "外系/跨系")</f>
+        <f>COUNTIFS(A6:A18, TRUE, H6:H18, "外系/跨系")</f>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -11644,7 +11644,7 @@
         <v/>
       </c>
       <c r="F26">
-        <f>=IF(AND(F21&gt;=8, F22&gt;=0, IF("true"="true", F25&gt;=1, TRUE)), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
+        <f>IF(AND(F21&gt;=8, F22&gt;=0, F25&gt;=1), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
       </c>
     </row>
   </sheetData>
@@ -11665,7 +11665,7 @@
     <col min="5" max="5" width="10.83203125" customWidth="1"/>
     <col min="6" max="6" width="10.83203125" customWidth="1"/>
     <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
     <col min="9" max="9" width="25.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -12026,7 +12026,7 @@
         <v>依學期開設</v>
       </c>
       <c r="H16" t="str">
-        <v>本系 (資管)</v>
+        <v>本系 (資訊管理系)</v>
       </c>
       <c r="I16" t="str">
         <v>專業選修</v>
@@ -12055,7 +12055,7 @@
         <v>依學期開設</v>
       </c>
       <c r="H17" t="str">
-        <v>本系 (資管)</v>
+        <v>本系 (資訊管理系)</v>
       </c>
       <c r="I17" t="str">
         <v>專業選修</v>
@@ -12084,7 +12084,7 @@
         <v>依學期開設</v>
       </c>
       <c r="H18" t="str">
-        <v>本系 (資管)</v>
+        <v>本系 (資訊管理系)</v>
       </c>
       <c r="I18" t="str">
         <v>專業選修</v>
@@ -12113,7 +12113,7 @@
         <v>依學期開設</v>
       </c>
       <c r="H19" t="str">
-        <v>本系 (資管)</v>
+        <v>本系 (資訊管理系)</v>
       </c>
       <c r="I19" t="str">
         <v>專業選修</v>
@@ -12142,7 +12142,7 @@
         <v>依學期開設</v>
       </c>
       <c r="H20" t="str">
-        <v>本系 (資管)</v>
+        <v>本系 (資訊管理系)</v>
       </c>
       <c r="I20" t="str">
         <v>專業選修</v>
@@ -12171,7 +12171,7 @@
         <v>依學期開設</v>
       </c>
       <c r="H21" t="str">
-        <v>本系 (資管)</v>
+        <v>本系 (資訊管理系)</v>
       </c>
       <c r="I21" t="str">
         <v>專業選修</v>
@@ -12200,7 +12200,7 @@
         <v>依學期開設</v>
       </c>
       <c r="H22" t="str">
-        <v>本系 (資管)</v>
+        <v>本系 (資訊管理系)</v>
       </c>
       <c r="I22" t="str">
         <v>專業選修</v>
@@ -12229,7 +12229,7 @@
         <v>依學期開設</v>
       </c>
       <c r="H23" t="str">
-        <v>本系 (資管)</v>
+        <v>本系 (資訊管理系)</v>
       </c>
       <c r="I23" t="str">
         <v>專業選修</v>
@@ -12258,7 +12258,7 @@
         <v>依學期開設</v>
       </c>
       <c r="H24" t="str">
-        <v>本系 (資管)</v>
+        <v>本系 (資訊管理系)</v>
       </c>
       <c r="I24" t="str">
         <v>專業選修</v>
@@ -12287,7 +12287,7 @@
         <v>依學期開設</v>
       </c>
       <c r="H25" t="str">
-        <v>本系 (資管)</v>
+        <v>本系 (資訊管理系)</v>
       </c>
       <c r="I25" t="str">
         <v>專業選修</v>
@@ -12316,7 +12316,7 @@
         <v>依學期開設</v>
       </c>
       <c r="H26" t="str">
-        <v>本系 (資管)</v>
+        <v>本系 (資訊管理系)</v>
       </c>
       <c r="I26" t="str">
         <v>專業選修</v>
@@ -12344,7 +12344,7 @@
         <v/>
       </c>
       <c r="F29">
-        <f>=SUMIF(A6:A26, TRUE, F6:F26)</f>
+        <f>SUMIF(A6:A26, TRUE, F6:F26)</f>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -12370,7 +12370,7 @@
         <v/>
       </c>
       <c r="F30">
-        <f>=SUMIFS(F6:F26, A6:A26, TRUE, E6:E26, "必修")</f>
+        <f>SUMIFS(F6:F26, A6:A26, TRUE, E6:E26, "必修")</f>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -12396,7 +12396,7 @@
         <v/>
       </c>
       <c r="F31">
-        <f>=SUMIFS(F6:F26, A6:A26, TRUE, E6:E26, "選修")</f>
+        <f>SUMIFS(F6:F26, A6:A26, TRUE, E6:E26, "選修")</f>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -12422,7 +12422,7 @@
         <v/>
       </c>
       <c r="F32">
-        <f>=SUMIFS(F6:F26, A6:A26, TRUE, H6:H26, "本系 (資管)")</f>
+        <f>SUMIFS(F6:F26, A6:A26, TRUE, H6:H26, "本系 (資訊管理系)")</f>
       </c>
     </row>
     <row r="33">
@@ -12442,7 +12442,7 @@
         <v/>
       </c>
       <c r="F33">
-        <f>=COUNTIFS(A6:A26, TRUE, H6:H26, "外系/跨系")</f>
+        <f>COUNTIFS(A6:A26, TRUE, H6:H26, "外系/跨系")</f>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -12468,7 +12468,7 @@
         <v/>
       </c>
       <c r="F34">
-        <f>=IF(AND(F29&gt;=8, F30&gt;=0, IF("true"="true", F33&gt;=1, TRUE)), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
+        <f>IF(AND(F29&gt;=8, F30&gt;=0, F33&gt;=1), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
       </c>
     </row>
   </sheetData>

--- a/public/downloads/NTUB_學分修業與證書資格試算表.xlsx
+++ b/public/downloads/NTUB_學分修業與證書資格試算表.xlsx
@@ -3,8 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="🎓證書資格審查總表" sheetId="1" r:id="rId1"/>
-    <sheet name="📋全校課程總表" sheetId="2" r:id="rId2"/>
+    <sheet name="證書資格審查總表" sheetId="1" r:id="rId1"/>
+    <sheet name="全校課程總表" sheetId="2" r:id="rId2"/>
     <sheet name="企業永續經營管理" sheetId="3" r:id="rId3"/>
     <sheet name="創新與創業管理" sheetId="4" r:id="rId4"/>
     <sheet name="外語與商務" sheetId="5" r:id="rId5"/>
@@ -14,8 +14,8 @@
     <sheet name="數據分析與視覺化" sheetId="9" r:id="rId9"/>
     <sheet name="社群媒體行銷" sheetId="10" r:id="rId10"/>
     <sheet name="東亞語言與商務" sheetId="11" r:id="rId11"/>
-    <sheet name="📖簡章設置要點" sheetId="12" r:id="rId12"/>
-    <sheet name="✏️自訂學分表" sheetId="13" r:id="rId13"/>
+    <sheet name="簡章設置要點" sheetId="12" r:id="rId12"/>
+    <sheet name="自訂學分表" sheetId="13" r:id="rId13"/>
   </sheets>
 </workbook>
 </file>
@@ -409,7 +409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M13"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
@@ -422,18 +422,18 @@
     <col min="9" max="9" width="14.83203125" customWidth="1"/>
     <col min="10" max="10" width="18.83203125" customWidth="1"/>
     <col min="11" max="11" width="14.83203125" customWidth="1"/>
-    <col min="12" max="12" width="34.83203125" customWidth="1"/>
+    <col min="12" max="12" width="30.83203125" customWidth="1"/>
     <col min="13" max="13" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>國立臺北商業大學 NTUB 學分學程暨微學程 — 修業證書資格審查總表 (Google Sheets / Excel 專用)</v>
+        <v>國立臺北商業大學 NTUB 學分學程暨微學程 — 修業證書資格審查總表</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>基準科系：資訊管理系（開課單位非資管系者自動判定為跨系/外系） ｜ 勾選各分頁的核取方塊即可即時試算</v>
+        <v>基準科系：資訊管理系（開課單位非資管系者自動判定為跨系/外系）</v>
       </c>
     </row>
     <row r="4">
@@ -471,7 +471,7 @@
         <v>跨系已修門數</v>
       </c>
       <c r="L4" t="str">
-        <v>證書取得資格判定 (公式即時連動)</v>
+        <v>證書取得資格判定</v>
       </c>
       <c r="M4" t="str">
         <v>所屬工作表分頁</v>
@@ -512,7 +512,7 @@
         <f>!F26</f>
       </c>
       <c r="L5">
-        <f>IF(AND(E5&gt;=D5, G5&gt;=F5, IF(J5="需跨修至少1門外系", K5&gt;=1, TRUE)), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
+        <f>IF(AND(E5&gt;=D5, G5&gt;=F5, IF(J5="需跨修至少1門外系", K5&gt;=1, TRUE)), "符合資格 (可申請證書)", "尚未達標 (學分不足或缺跨系)")</f>
       </c>
       <c r="M5" t="str">
         <v>企業永續經營管理</v>
@@ -553,7 +553,7 @@
         <f>!F27</f>
       </c>
       <c r="L6">
-        <f>IF(AND(E6&gt;=D6, G6&gt;=F6, IF(J6="需跨修至少1門外系", K6&gt;=1, TRUE)), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
+        <f>IF(AND(E6&gt;=D6, G6&gt;=F6, IF(J6="需跨修至少1門外系", K6&gt;=1, TRUE)), "符合資格 (可申請證書)", "尚未達標 (學分不足或缺跨系)")</f>
       </c>
       <c r="M6" t="str">
         <v>創新與創業管理</v>
@@ -594,7 +594,7 @@
         <f>!F39</f>
       </c>
       <c r="L7">
-        <f>IF(AND(E7&gt;=D7, G7&gt;=F7, IF(J7="需跨修至少1門外系", K7&gt;=1, TRUE)), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
+        <f>IF(AND(E7&gt;=D7, G7&gt;=F7, IF(J7="需跨修至少1門外系", K7&gt;=1, TRUE)), "符合資格 (可申請證書)", "尚未達標 (學分不足或缺跨系)")</f>
       </c>
       <c r="M7" t="str">
         <v>外語與商務</v>
@@ -635,7 +635,7 @@
         <f>!F26</f>
       </c>
       <c r="L8">
-        <f>IF(AND(E8&gt;=D8, G8&gt;=F8, IF(J8="需跨修至少1門外系", K8&gt;=1, TRUE)), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
+        <f>IF(AND(E8&gt;=D8, G8&gt;=F8, IF(J8="需跨修至少1門外系", K8&gt;=1, TRUE)), "符合資格 (可申請證書)", "尚未達標 (學分不足或缺跨系)")</f>
       </c>
       <c r="M8" t="str">
         <v>大數據</v>
@@ -676,7 +676,7 @@
         <f>!F30</f>
       </c>
       <c r="L9">
-        <f>IF(AND(E9&gt;=D9, G9&gt;=F9, IF(J9="需跨修至少1門外系", K9&gt;=1, TRUE)), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
+        <f>IF(AND(E9&gt;=D9, G9&gt;=F9, IF(J9="需跨修至少1門外系", K9&gt;=1, TRUE)), "符合資格 (可申請證書)", "尚未達標 (學分不足或缺跨系)")</f>
       </c>
       <c r="M9" t="str">
         <v>數位行銷</v>
@@ -717,7 +717,7 @@
         <f>!F25</f>
       </c>
       <c r="L10">
-        <f>IF(AND(E10&gt;=D10, G10&gt;=F10, IF(J10="需跨修至少1門外系", K10&gt;=1, TRUE)), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
+        <f>IF(AND(E10&gt;=D10, G10&gt;=F10, IF(J10="需跨修至少1門外系", K10&gt;=1, TRUE)), "符合資格 (可申請證書)", "尚未達標 (學分不足或缺跨系)")</f>
       </c>
       <c r="M10" t="str">
         <v>數位行銷與語言科技應用</v>
@@ -758,7 +758,7 @@
         <f>!F33</f>
       </c>
       <c r="L11">
-        <f>IF(AND(E11&gt;=D11, G11&gt;=F11, IF(J11="需跨修至少1門外系", K11&gt;=1, TRUE)), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
+        <f>IF(AND(E11&gt;=D11, G11&gt;=F11, IF(J11="需跨修至少1門外系", K11&gt;=1, TRUE)), "符合資格 (可申請證書)", "尚未達標 (學分不足或缺跨系)")</f>
       </c>
       <c r="M11" t="str">
         <v>數據分析與視覺化</v>
@@ -799,7 +799,7 @@
         <f>!F26</f>
       </c>
       <c r="L12">
-        <f>IF(AND(E12&gt;=D12, G12&gt;=F12, IF(J12="需跨修至少1門外系", K12&gt;=1, TRUE)), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
+        <f>IF(AND(E12&gt;=D12, G12&gt;=F12, IF(J12="需跨修至少1門外系", K12&gt;=1, TRUE)), "符合資格 (可申請證書)", "尚未達標 (學分不足或缺跨系)")</f>
       </c>
       <c r="M12" t="str">
         <v>社群媒體行銷</v>
@@ -840,30 +840,15 @@
         <f>!F30</f>
       </c>
       <c r="L13">
-        <f>IF(AND(E13&gt;=D13, G13&gt;=F13, IF(J13="需跨修至少1門外系", K13&gt;=1, TRUE)), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
+        <f>IF(AND(E13&gt;=D13, G13&gt;=F13, IF(J13="需跨修至少1門外系", K13&gt;=1, TRUE)), "符合資格 (可申請證書)", "尚未達標 (學分不足或缺跨系)")</f>
       </c>
       <c r="M13" t="str">
         <v>東亞語言與商務</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>--- 💡 Google Sheets / Excel 使用小秘訣 ---</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>1. 本試算表在 Google Sheets 中可將 A 欄核取方塊（TRUE / FALSE）直接打勾，所有加總與證書審查公式將全自動即時更新！</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>2. 點擊下方各分頁標籤（如「巨量資料」、「數位行銷」等），可分別查看各學程專屬修課清單。</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -872,7 +857,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I27"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
     <col min="3" max="3" width="32.83203125" customWidth="1"/>
     <col min="4" max="4" width="18.83203125" customWidth="1"/>
@@ -900,7 +885,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>修業狀態 (核取方塊)</v>
+        <v>修業狀態</v>
       </c>
       <c r="B5" t="str">
         <v>課程代碼</v>
@@ -1479,7 +1464,7 @@
         <v/>
       </c>
       <c r="F27">
-        <f>IF(AND(F22&gt;=12, F23&gt;=0, F26&gt;=1), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
+        <f>IF(AND(F22&gt;=12, F23&gt;=0, F26&gt;=1), "符合資格 (可申請證書)", "尚未達標 (學分不足或缺跨系)")</f>
       </c>
     </row>
   </sheetData>
@@ -1493,7 +1478,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I31"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
     <col min="3" max="3" width="32.83203125" customWidth="1"/>
     <col min="4" max="4" width="18.83203125" customWidth="1"/>
@@ -1521,7 +1506,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>修業狀態 (核取方塊)</v>
+        <v>修業狀態</v>
       </c>
       <c r="B5" t="str">
         <v>課程代碼</v>
@@ -2216,7 +2201,7 @@
         <v/>
       </c>
       <c r="F31">
-        <f>IF(AND(F26&gt;=8, F27&gt;=0, F30&gt;=1), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
+        <f>IF(AND(F26&gt;=8, F27&gt;=0, F30&gt;=1), "符合資格 (可申請證書)", "尚未達標 (學分不足或缺跨系)")</f>
       </c>
     </row>
   </sheetData>
@@ -2583,7 +2568,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H12"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
     <col min="3" max="3" width="30.83203125" customWidth="1"/>
     <col min="4" max="4" width="18.83203125" customWidth="1"/>
@@ -2600,12 +2585,12 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>A 欄為核取方塊 (TRUE 已修 / FALSE 未修)</v>
+        <v>修業狀態欄為核取方塊 (TRUE 已修 / FALSE 未修)</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>修業狀態 (核取方塊)</v>
+        <v>修業狀態</v>
       </c>
       <c r="B4" t="str">
         <v>課程代碼</v>
@@ -2801,7 +2786,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I165"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
     <col min="3" max="3" width="32.83203125" customWidth="1"/>
     <col min="4" max="4" width="18.83203125" customWidth="1"/>
@@ -2819,12 +2804,12 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>A 欄為核取方塊 (勾選 TRUE 代表已修畢，取消 FALSE 代表未修) ｜ 開課單位非資管系者自動為跨系/外系</v>
+        <v>修業狀態欄為核取方塊 (勾選 TRUE 代表已修畢，取消 FALSE 代表未修) ｜ 開課單位非資管系者自動為跨系/外系</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>修業狀態 (核取方塊)</v>
+        <v>修業狀態</v>
       </c>
       <c r="B4" t="str">
         <v>課程代碼</v>
@@ -7439,7 +7424,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I27"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
     <col min="3" max="3" width="32.83203125" customWidth="1"/>
     <col min="4" max="4" width="18.83203125" customWidth="1"/>
@@ -7467,7 +7452,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>修業狀態 (核取方塊)</v>
+        <v>修業狀態</v>
       </c>
       <c r="B5" t="str">
         <v>課程代碼</v>
@@ -8046,7 +8031,7 @@
         <v/>
       </c>
       <c r="F27">
-        <f>IF(AND(F22&gt;=15, F23&gt;=2, F26&gt;=1), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
+        <f>IF(AND(F22&gt;=15, F23&gt;=2, F26&gt;=1), "符合資格 (可申請證書)", "尚未達標 (學分不足或缺跨系)")</f>
       </c>
     </row>
   </sheetData>
@@ -8060,7 +8045,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I28"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
     <col min="3" max="3" width="32.83203125" customWidth="1"/>
     <col min="4" max="4" width="18.83203125" customWidth="1"/>
@@ -8088,7 +8073,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>修業狀態 (核取方塊)</v>
+        <v>修業狀態</v>
       </c>
       <c r="B5" t="str">
         <v>課程代碼</v>
@@ -8696,7 +8681,7 @@
         <v/>
       </c>
       <c r="F28">
-        <f>IF(AND(F23&gt;=15, F24&gt;=2, F27&gt;=1), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
+        <f>IF(AND(F23&gt;=15, F24&gt;=2, F27&gt;=1), "符合資格 (可申請證書)", "尚未達標 (學分不足或缺跨系)")</f>
       </c>
     </row>
   </sheetData>
@@ -8710,7 +8695,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I40"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
     <col min="3" max="3" width="32.83203125" customWidth="1"/>
     <col min="4" max="4" width="18.83203125" customWidth="1"/>
@@ -8738,7 +8723,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>修業狀態 (核取方塊)</v>
+        <v>修業狀態</v>
       </c>
       <c r="B5" t="str">
         <v>課程代碼</v>
@@ -9694,7 +9679,7 @@
         <v/>
       </c>
       <c r="F40">
-        <f>IF(AND(F35&gt;=15, F36&gt;=0, F39&gt;=1), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
+        <f>IF(AND(F35&gt;=15, F36&gt;=0, F39&gt;=1), "符合資格 (可申請證書)", "尚未達標 (學分不足或缺跨系)")</f>
       </c>
     </row>
   </sheetData>
@@ -9708,7 +9693,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I27"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
     <col min="3" max="3" width="32.83203125" customWidth="1"/>
     <col min="4" max="4" width="18.83203125" customWidth="1"/>
@@ -9736,7 +9721,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>修業狀態 (核取方塊)</v>
+        <v>修業狀態</v>
       </c>
       <c r="B5" t="str">
         <v>課程代碼</v>
@@ -10315,7 +10300,7 @@
         <v/>
       </c>
       <c r="F27">
-        <f>IF(AND(F22&gt;=8, F23&gt;=0, F26&gt;=1), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
+        <f>IF(AND(F22&gt;=8, F23&gt;=0, F26&gt;=1), "符合資格 (可申請證書)", "尚未達標 (學分不足或缺跨系)")</f>
       </c>
     </row>
   </sheetData>
@@ -10329,7 +10314,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I31"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
     <col min="3" max="3" width="32.83203125" customWidth="1"/>
     <col min="4" max="4" width="18.83203125" customWidth="1"/>
@@ -10357,7 +10342,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>修業狀態 (核取方塊)</v>
+        <v>修業狀態</v>
       </c>
       <c r="B5" t="str">
         <v>課程代碼</v>
@@ -11052,7 +11037,7 @@
         <v/>
       </c>
       <c r="F31">
-        <f>IF(AND(F26&gt;=15, F27&gt;=2, F30&gt;=1), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
+        <f>IF(AND(F26&gt;=15, F27&gt;=2, F30&gt;=1), "符合資格 (可申請證書)", "尚未達標 (學分不足或缺跨系)")</f>
       </c>
     </row>
   </sheetData>
@@ -11066,7 +11051,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I26"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
     <col min="3" max="3" width="32.83203125" customWidth="1"/>
     <col min="4" max="4" width="18.83203125" customWidth="1"/>
@@ -11094,7 +11079,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>修業狀態 (核取方塊)</v>
+        <v>修業狀態</v>
       </c>
       <c r="B5" t="str">
         <v>課程代碼</v>
@@ -11644,7 +11629,7 @@
         <v/>
       </c>
       <c r="F26">
-        <f>IF(AND(F21&gt;=8, F22&gt;=0, F25&gt;=1), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
+        <f>IF(AND(F21&gt;=8, F22&gt;=0, F25&gt;=1), "符合資格 (可申請證書)", "尚未達標 (學分不足或缺跨系)")</f>
       </c>
     </row>
   </sheetData>
@@ -11658,7 +11643,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I34"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
     <col min="3" max="3" width="32.83203125" customWidth="1"/>
     <col min="4" max="4" width="18.83203125" customWidth="1"/>
@@ -11686,7 +11671,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>修業狀態 (核取方塊)</v>
+        <v>修業狀態</v>
       </c>
       <c r="B5" t="str">
         <v>課程代碼</v>
@@ -12468,7 +12453,7 @@
         <v/>
       </c>
       <c r="F34">
-        <f>IF(AND(F29&gt;=8, F30&gt;=0, F33&gt;=1), "🟢 ✓ 符合資格 (可申請證書)", "🔴 尚未達標 (學分不足或缺跨系)")</f>
+        <f>IF(AND(F29&gt;=8, F30&gt;=0, F33&gt;=1), "符合資格 (可申請證書)", "尚未達標 (學分不足或缺跨系)")</f>
       </c>
     </row>
   </sheetData>
